--- a/results/tables/sheet_inventory.xlsx
+++ b/results/tables/sheet_inventory.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,124 +379,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fig 4</t>
+          <t>Fig 3</t>
         </is>
       </c>
       <c r="B2">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>figure_4a_72h_imaging, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21</t>
+          <t>fig_3_72h_imaging, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fig 5</t>
+          <t>Fig 4</t>
         </is>
       </c>
       <c r="B3">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>figure_5a, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22</t>
+          <t>figure_4a_72h_imaging, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fig6_PA</t>
+          <t>Fig_4_Ehsan</t>
         </is>
       </c>
       <c r="B4">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flow_time, treat, npm1_genot, dosage, rel_p_syk</t>
+          <t>sample_id, a_pd1, entospletinib, jq1, venetoclax, palbociclib, sorafenib, gw_2580, bez235, mk_2206, trametinib, doramapimod, cyt387, n_fk_b_act_inhib, dasatinib, panobinostat, nvp_tae684, olaparib, pd173074, ibrutinib, a_cd3_ms_ig_g</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fig 6</t>
+          <t>Fig 5</t>
         </is>
       </c>
       <c r="B5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>only_graphing_5u_m_dose_for_the_figure_b_c_we_dont_have_complete_data_for_the_lower_doses_in_the_pv_treated_conditions, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21</t>
+          <t>figure_5a, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fig 7</t>
+          <t>Fig 6</t>
         </is>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fig_7a_72h_mts_data, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22, x23</t>
+          <t>only_graphing_5u_m_dose_for_the_figure_b_c_we_dont_have_complete_data_for_the_lower_doses_in_the_pv_treated_conditions, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fig 8</t>
+          <t>Fig 7</t>
         </is>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>figure_8a_t_cells_72h_imaging, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22</t>
+          <t>fig_7a_72h_mts_data, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22, x23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Fig 8</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>figure_8a_t_cells_72h_imaging, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Fig Supp1</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>109</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>23</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>only_graphing_5u_m_dose_for_the_figure_to_make_the_point_more_obvious_also_we_dont_have_complete_data_for_the_lower_doses_in_the_pv_treated_conditions, x2, x3, x4, x5, x6, x7, x8, x9, x10, x11, x12, x13, x14, x15, x16, x17, x18, x19, x20, x21, x22, x23</t>
         </is>
